--- a/Correção Alejandra.xlsx
+++ b/Correção Alejandra.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desktop\Desktop\SENAI\02 - Disciplinas\03 - PWBE\02 - PWBE 2DS\04 - Integrador\Projetos da turma 20\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desktop\Desktop\SENAI\02 - Disciplinas\03 - PWBE\02 - PWBE 2DS\04 - Integrador\Projetos da turma 20\Alejandra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A520DF7-EBD2-4371-BE9D-65372CB5B74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9154C3-E788-4530-9F38-98E69DF1A72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,9 +129,6 @@
     <t>Total críticos:</t>
   </si>
   <si>
-    <t>49/50</t>
-  </si>
-  <si>
     <t>CRITÉRIOS DESEJÁVEIS (50 pts)</t>
   </si>
   <si>
@@ -246,18 +243,12 @@
     <t>Total desejáveis:</t>
   </si>
   <si>
-    <t>43/50</t>
-  </si>
-  <si>
     <t>'4/4</t>
   </si>
   <si>
     <t>'6/6</t>
   </si>
   <si>
-    <t>'1/2</t>
-  </si>
-  <si>
     <t>'8/8</t>
   </si>
   <si>
@@ -276,9 +267,6 @@
     <t>'3/3</t>
   </si>
   <si>
-    <t>'2/4</t>
-  </si>
-  <si>
     <t>'0/1</t>
   </si>
   <si>
@@ -292,6 +280,18 @@
   </si>
   <si>
     <t xml:space="preserve">Nota </t>
+  </si>
+  <si>
+    <t>2/2</t>
+  </si>
+  <si>
+    <t>50/50</t>
+  </si>
+  <si>
+    <t>4/4</t>
+  </si>
+  <si>
+    <t>45/50</t>
   </si>
 </sst>
 </file>
@@ -702,7 +702,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -716,7 +716,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>9</v>
@@ -730,7 +730,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>11</v>
@@ -743,8 +743,8 @@
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>75</v>
+      <c r="C7" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
@@ -758,7 +758,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>15</v>
@@ -772,7 +772,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -786,7 +786,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>19</v>
@@ -800,7 +800,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -814,7 +814,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>23</v>
@@ -828,7 +828,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
@@ -842,7 +842,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>27</v>
@@ -856,7 +856,7 @@
         <v>28</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>29</v>
@@ -870,13 +870,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -892,7 +892,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.25">
@@ -900,7 +900,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -922,13 +922,13 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" t="s">
         <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,13 +936,13 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" t="s">
         <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -950,13 +950,13 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
         <v>39</v>
-      </c>
-      <c r="C25" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -964,13 +964,13 @@
         <v>17</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -978,13 +978,13 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" t="s">
         <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -992,13 +992,13 @@
         <v>19</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1006,13 +1006,13 @@
         <v>20</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,13 +1020,13 @@
         <v>21</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1034,13 +1034,13 @@
         <v>22</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1048,13 +1048,13 @@
         <v>23</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1062,13 +1062,13 @@
         <v>24</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1076,13 +1076,13 @@
         <v>25</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1090,13 +1090,13 @@
         <v>26</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1104,13 +1104,13 @@
         <v>27</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1118,13 +1118,13 @@
         <v>28</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1132,13 +1132,13 @@
         <v>29</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,13 +1146,13 @@
         <v>30</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1160,18 +1160,18 @@
         <v>31</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1196,13 +1196,13 @@
         <v>29</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1210,13 +1210,13 @@
         <v>30</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1224,31 +1224,31 @@
         <v>31</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B52" s="8">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
